--- a/docs/ksr/최종정리_1차/14_요구사항정의서_최종_2026-10-21(답변반영건10-22).xlsx
+++ b/docs/ksr/최종정리_1차/14_요구사항정의서_최종_2026-10-21(답변반영건10-22).xlsx
@@ -4367,7 +4367,7 @@
       <c r="J12" s="34" t="inlineStr">
         <is>
           <t>2026-10-21 기준 화면. 품목 분기 결과와 일반 결과 두 경로 모두에 「이 문장 고쳐 쓰기」가 붙는다(10-06 병합 주의 해소). 인코더 추정 유형만 있는 문장도 고쳐 쓴다. 결과는 다듬은 안 · 담백한 안 · 조건부 후보이고 각각 다시 판정 · 복사가 있다. 고친 문구는 고른 전제를 입력으로 다시 판정한다(앞서 한 답은 기준 커밋에서는 싣지 않았고, 10-22 `6fec0bc` 부터 함께 싣는다). 서버가 없으면 후보를 지어내지 않고 「고쳐 쓰기 서버(sLLM)에 연결하지 못했어요 — 후보를 만들지 않았어요」 · 「이 환경에서는 문장 고쳐 쓰기를 제공하지 않아요」를 낸다. sLLM 은 별도 서버(127.0.0.1:8765 · 1단계 q4b-v14 잠금 · 2단계 다듬기는 규칙판이 기본이고 잠금된 persona_q4b_polish 는 되돌림 · 고객층 말투 전용).
-2026-10-21 서비스 시험(12 보고서 E-01)은 sLLM 서버가 없는 상태의 안내만 확인했다 — 서버가 있을 때의 후보 · 재판정은 이 시험에서 확인하지 못했다.
+2026-10-21 서비스 시험(12 보고서 E-01)은 sLLM 서버가 없는 상태의 안내만 확인했다. 서버가 있을 때의 후보 · 재판정은 2026-10-22 배포 서버(copylane.site · 비회원 검수 · 식품 → 일반식품) 화면에서 확인했다 — 다듬은 안 · 담백한 안과 각 다시 판정이 나온다(11 그림 8-1).
 화면 문구의 결정 번호(D-59 · D-146 · D-119)는 10-22 `6fec0bc` 로 걷었다(기준 커밋 뒤).</t>
         </is>
       </c>
